--- a/resultados/third_review/20260907_data2024_table4_medication_categories.xlsx
+++ b/resultados/third_review/20260907_data2024_table4_medication_categories.xlsx
@@ -33,12 +33,12 @@
     <t xml:space="preserve">Octreotide without lanreotide</t>
   </si>
   <si>
+    <t xml:space="preserve">Lanreotide without octreotide</t>
+  </si>
+  <si>
     <t xml:space="preserve">No somatostatin analogue (cabergoline only)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lanreotide without octreotide</t>
-  </si>
-  <si>
     <t xml:space="preserve">Both analogues (octreotide and lanreotide)</t>
   </si>
   <si>
@@ -51,10 +51,10 @@
     <t xml:space="preserve">patients</t>
   </si>
   <si>
+    <t xml:space="preserve">Octreotide only</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cabergoline only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octreotide only</t>
   </si>
   <si>
     <t xml:space="preserve">Lanreotide only</t>
@@ -420,16 +420,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>270</v>
+        <v>446</v>
       </c>
       <c r="C2" t="n">
-        <v>1344</v>
+        <v>1313</v>
       </c>
       <c r="D2" t="n">
-        <v>1614</v>
+        <v>1759</v>
       </c>
       <c r="E2" t="n">
-        <v>38.1</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="3">
@@ -437,16 +437,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>1497</v>
+        <v>424</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>776</v>
       </c>
       <c r="D3" t="n">
-        <v>1497</v>
+        <v>1200</v>
       </c>
       <c r="E3" t="n">
-        <v>35.4</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="4">
@@ -454,16 +454,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>240</v>
+        <v>1188</v>
       </c>
       <c r="C4" t="n">
-        <v>820</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1060</v>
+        <v>1188</v>
       </c>
       <c r="E4" t="n">
-        <v>25.1</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="5">
@@ -471,16 +471,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -523,10 +523,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>1497</v>
+        <v>1313</v>
       </c>
       <c r="C2" t="n">
-        <v>35.4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -534,10 +534,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>1344</v>
+        <v>1188</v>
       </c>
       <c r="C3" t="n">
-        <v>31.8</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="n">
-        <v>820</v>
+        <v>776</v>
       </c>
       <c r="C4" t="n">
-        <v>19.4</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>270</v>
+        <v>446</v>
       </c>
       <c r="C5" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="6">
@@ -567,10 +567,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>240</v>
+        <v>424</v>
       </c>
       <c r="C6" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         <v>17</v>
       </c>
       <c r="B7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" t="n">
         <v>1.1</v>
@@ -589,10 +589,10 @@
         <v>18</v>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
